--- a/Test Results/Excel/Summary_Report.xlsx
+++ b/Test Results/Excel/Summary_Report.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 19:12:30 UTC</t>
+          <t>2026-10-28 14:26:43 UTC</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>470</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>470</v>
+        <v>506</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -552,7 +552,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>99.22%</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>74.39s</t>
+          <t>0.73s</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/Summary_Report.xlsx
+++ b/Test Results/Excel/Summary_Report.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 14:26:43 UTC</t>
+          <t>2026-10-28 15:40:29 UTC</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -552,7 +552,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>99.22%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>0.73s</t>
+          <t>0.31s</t>
         </is>
       </c>
     </row>
